--- a/artfynd/A 7921-2026 artfynd.xlsx
+++ b/artfynd/A 7921-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,6 +1213,2015 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131523925</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>369223</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6870745</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131523923</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>369348</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6870729</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131523924</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>369258</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6870749</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131523931</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>369324</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6870710</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131523933</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>369569</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6870574</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131523934</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>369627</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6870559</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131523929</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>369307</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6870734</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131523905</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80356</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>369606</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6870601</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131523907</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57079</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>369547</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6870562</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131523864</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>369453</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6870616</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131523930</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>369318</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6870721</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131523896</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>369418</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6870664</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131523953</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79007</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>369447</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6870623</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131523932</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>369392</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6870685</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131523927</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>369245</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6870702</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131523922</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>369483</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6870580</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131523895</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>369239</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6870699</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131523928</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>369288</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6870727</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131523935</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vassbo gruva, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>369620</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6870560</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7921-2026 artfynd.xlsx
+++ b/artfynd/A 7921-2026 artfynd.xlsx
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131523907</v>
+        <v>131523864</v>
       </c>
       <c r="B14" t="n">
-        <v>57079</v>
+        <v>57076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>369547</v>
+        <v>369453</v>
       </c>
       <c r="R14" t="n">
-        <v>6870562</v>
+        <v>6870616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131523864</v>
+        <v>131523907</v>
       </c>
       <c r="B15" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>369453</v>
+        <v>369547</v>
       </c>
       <c r="R15" t="n">
-        <v>6870616</v>
+        <v>6870562</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 7921-2026 artfynd.xlsx
+++ b/artfynd/A 7921-2026 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>131523925</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131523923</v>
+        <v>131523924</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>369348</v>
+        <v>369258</v>
       </c>
       <c r="R7" t="n">
-        <v>6870729</v>
+        <v>6870749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131523924</v>
+        <v>131523923</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369258</v>
+        <v>369348</v>
       </c>
       <c r="R8" t="n">
-        <v>6870749</v>
+        <v>6870729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131523931</v>
+        <v>131523933</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>369324</v>
+        <v>369569</v>
       </c>
       <c r="R9" t="n">
-        <v>6870710</v>
+        <v>6870574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131523933</v>
+        <v>131523931</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>369569</v>
+        <v>369324</v>
       </c>
       <c r="R10" t="n">
-        <v>6870574</v>
+        <v>6870710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
         <v>131523934</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,43 +1857,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131523929</v>
+        <v>131523905</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>80359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1901,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>369307</v>
+        <v>369606</v>
       </c>
       <c r="R12" t="n">
-        <v>6870734</v>
+        <v>6870601</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,37 +1958,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131523905</v>
+        <v>131523929</v>
       </c>
       <c r="B13" t="n">
-        <v>80356</v>
+        <v>8453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>369606</v>
+        <v>369307</v>
       </c>
       <c r="R13" t="n">
-        <v>6870601</v>
+        <v>6870734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2068,7 +2068,7 @@
         <v>131523864</v>
       </c>
       <c r="B14" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>131523907</v>
       </c>
       <c r="B15" t="n">
-        <v>57079</v>
+        <v>57082</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>131523930</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>131523896</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>131523953</v>
       </c>
       <c r="B18" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>131523932</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>131523927</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>131523922</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131523895</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>131523928</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>131523935</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 7921-2026 artfynd.xlsx
+++ b/artfynd/A 7921-2026 artfynd.xlsx
@@ -1322,7 +1322,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131523924</v>
+        <v>131523923</v>
       </c>
       <c r="B7" t="n">
         <v>8453</v>
@@ -1356,7 +1356,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>369258</v>
+        <v>369348</v>
       </c>
       <c r="R7" t="n">
-        <v>6870749</v>
+        <v>6870729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131523923</v>
+        <v>131523924</v>
       </c>
       <c r="B8" t="n">
         <v>8453</v>
@@ -1463,7 +1463,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>369348</v>
+        <v>369258</v>
       </c>
       <c r="R8" t="n">
-        <v>6870729</v>
+        <v>6870749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131523933</v>
+        <v>131523931</v>
       </c>
       <c r="B9" t="n">
         <v>8453</v>
@@ -1570,7 +1570,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>369569</v>
+        <v>369324</v>
       </c>
       <c r="R9" t="n">
-        <v>6870574</v>
+        <v>6870710</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131523931</v>
+        <v>131523933</v>
       </c>
       <c r="B10" t="n">
         <v>8453</v>
@@ -1677,7 +1677,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>369324</v>
+        <v>369569</v>
       </c>
       <c r="R10" t="n">
-        <v>6870710</v>
+        <v>6870574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1860,7 +1860,7 @@
         <v>131523905</v>
       </c>
       <c r="B12" t="n">
-        <v>80359</v>
+        <v>80360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131523864</v>
+        <v>131523907</v>
       </c>
       <c r="B14" t="n">
-        <v>57079</v>
+        <v>57083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,21 +2076,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2098,7 +2098,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>369453</v>
+        <v>369547</v>
       </c>
       <c r="R14" t="n">
-        <v>6870616</v>
+        <v>6870562</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131523907</v>
+        <v>131523864</v>
       </c>
       <c r="B15" t="n">
-        <v>57082</v>
+        <v>57080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>369547</v>
+        <v>369453</v>
       </c>
       <c r="R15" t="n">
-        <v>6870562</v>
+        <v>6870616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2385,7 +2385,7 @@
         <v>131523896</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>131523953</v>
       </c>
       <c r="B18" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>131523895</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131523928</v>
+        <v>131523935</v>
       </c>
       <c r="B23" t="n">
         <v>8453</v>
@@ -3044,7 +3044,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>369288</v>
+        <v>369620</v>
       </c>
       <c r="R23" t="n">
-        <v>6870727</v>
+        <v>6870560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131523935</v>
+        <v>131523928</v>
       </c>
       <c r="B24" t="n">
         <v>8453</v>
@@ -3151,7 +3151,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>369620</v>
+        <v>369288</v>
       </c>
       <c r="R24" t="n">
-        <v>6870560</v>
+        <v>6870727</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
